--- a/outputs/Stoke Park School - Glass Sizes vs Quoted Glass (check).xlsx
+++ b/outputs/Stoke Park School - Glass Sizes vs Quoted Glass (check).xlsx
@@ -9,8 +9,10 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Per type" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aplus final list" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vetroseal 064542" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Louvres not glass" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pane sizes quoted v final" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aplus final list" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vetroseal 064542" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -49,12 +51,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4E4"/>
+        <fgColor rgb="001F2A44"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F2A44"/>
+        <fgColor rgb="00FCE4E4"/>
       </patternFill>
     </fill>
   </fills>
@@ -73,11 +75,11 @@
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -443,7 +445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -524,210 +526,302 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Panes required (Aplus final)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>170</v>
-      </c>
+          <t>QUANTITY - no shortfall</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Panes on Vetroseal quote</t>
+          <t>Panes on Aplus final list</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>124</v>
+        <v>170</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Shortfall (panes)</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>46</v>
+          <t>less LOUVRE positions (IKON, not glass)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>46 / 23.84 m2</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Area required m2</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>130.81</v>
+          <t>GLASS required</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>124 / 106.97 m2</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Area on Vetroseal quote m2</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>105.24</v>
+          <t>Panes on Vetroseal quote</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>124 / 105.24 m2</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Shortfall m2</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>25.57</v>
+          <t>Difference</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>+0 panes / -1.73 m2</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Shortfall %</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>24.3%</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
+      <c r="B15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>SIZE - every quoted pane is superseded</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Vetroseal goods value quoted</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>11576.36</v>
+          <t>Quoted panes matching a final-list size</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0 of 124</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vetroseal rate implied GBP/m2</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>110</v>
+          <t>Why</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>job re-input at Aplus 02/07/2026; both buys predate it</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Vetroseal energy surcharge GBP/m2</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4.15</v>
-      </c>
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Vetroseal quoted net (goods+surcharge)</t>
+          <t>Vetroseal goods value quoted</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>12012.88</v>
+        <v>11576.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Same rate on final area - indicative net</t>
+          <t>Vetroseal rate implied GBP/m2</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14931.12</v>
+        <v>110</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Indicative increase</t>
+          <t>Vetroseal energy surcharge GBP/m2</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>2918.24</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CN Glass GBP 60/m2 on final area</t>
+          <t>Vetroseal quoted net (goods+surcharge)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7848.48</v>
+        <v>12012.88</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Same rate on glass area - indicative net</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>12209.84</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>28mm panes / m2 required</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>161 / 122.48</t>
-        </is>
+          <t>Indicative increase</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>196.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>32mm panes / m2 required</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>9 / 8.33</t>
-        </is>
+          <t>CN Glass GBP 60/m2 on the 28mm glass only</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>6150.72</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>32mm on Vetroseal quote</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NONE - every line quoted 8.8L-16-4T (28.8mm)</t>
-        </is>
-      </c>
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Panes excluded</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>0 marked DO NOT ORDER - Unglazed (aluminium infill panels)</t>
-        </is>
+          <t>COST vs THE SOLD PRICE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Glass carried in the price (Vetroseal 063934, 05/06)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>9309.219999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Indicative figures use Vetroseal's own quoted rate on the larger area. They are NOT a quote -</t>
-        </is>
+          <t>Glass now quoted (Vetroseal 064542, 01/07)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>12012.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
+        <is>
+          <t>Louvres carried in the price (IKON Q26-24160, 05/06)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>7490.64</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Louvres now quoted (IKON Q26-24329, 02/07)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>10125.91</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Cost above the sold price</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>5338.93</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>28mm GLASS panes / m2 required</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>118 / 102.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>32mm GLASS panes / m2 required</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>6 / 4.46</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>32mm on Vetroseal quote</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>NONE - every line quoted 8.8L-16-4T (28.8mm)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Panes excluded</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0 marked DO NOT ORDER - Unglazed (aluminium infill panels)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Indicative figures use Vetroseal's own quoted rate on the larger area. They are NOT a quote -</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>the 32mm make-up is unpriced and glass rates move with area, weight and pane size.</t>
         </is>
@@ -744,7 +838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -770,7 +864,7 @@
       </c>
       <c r="C1" s="2" t="inlineStr">
         <is>
-          <t>Panes required</t>
+          <t>Glass required</t>
         </is>
       </c>
       <c r="D1" s="2" t="inlineStr">
@@ -780,12 +874,12 @@
       </c>
       <c r="E1" s="2" t="inlineStr">
         <is>
-          <t>Shortfall</t>
+          <t>Difference</t>
         </is>
       </c>
       <c r="F1" s="2" t="inlineStr">
         <is>
-          <t>Area required m2</t>
+          <t>Glass area m2</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -830,397 +924,361 @@
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Door Type B1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>TYPE/B1/D02</t>
         </is>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="C3" t="n">
+        <v>2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>A5, F5</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Door Type B2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D04/TYPE/B2</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>A5, F5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Door Type D</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>TYPE/d</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>3</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>A1, A5, F5</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>head/transom pane missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Door Type B2</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>D04/TYPE/B2</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="3" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>A1, A5, F5</t>
-        </is>
-      </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>head/transom pane missing</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>Door Type C</t>
-        </is>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>(not on quote)</t>
-        </is>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F5" s="3" t="n">
-        <v>4.59</v>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t>A1, A5, F5</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>not on the quote at all</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Door Type D</t>
+          <t>Type A</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>TYPE/d</t>
+          <t>TYPE/A</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>4.59</v>
+        <v>4.97</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A1, A5, F5</t>
+          <t>A4, A8</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Type A</t>
-        </is>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>TYPE/A</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="n">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="F7" s="3" t="n">
-        <v>6.19</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>A1, A4, A8</t>
-        </is>
-      </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>one pane per bay missing (ref A1 toplight)</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>TYPE/B</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>8</v>
+      </c>
+      <c r="D7" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>6.66</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>A4, A8</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Type B</t>
-        </is>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>TYPE/B</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>TYPE/C</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>40</v>
+      </c>
+      <c r="D8" t="n">
+        <v>40</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>A4, A8</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TYPE/D</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>4</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>A1, A4, A8</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>one pane per bay missing (ref A1 toplight)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Type C</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>TYPE/C</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="n">
-        <v>60</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>40</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>41.6</v>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
-        <is>
-          <t>A1, A4, A8</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>one pane per bay missing (ref A1 toplight)</t>
-        </is>
-      </c>
+      <c r="D9" t="n">
+        <v>4</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>A4, A8</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Type D</t>
-        </is>
-      </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>TYPE/D</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="3" t="n">
-        <v>3.63</v>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>A1, A4, A8</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>one pane per bay missing (ref A1 toplight)</t>
-        </is>
-      </c>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Type E</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>TYPE/E</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Type E</t>
+          <t>Type F</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>TYPE/E</t>
+          <t>TYPE/F</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.86</v>
+        <v>11.26</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A1</t>
+          <t>A4, A8</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>Type F</t>
-        </is>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
-        <is>
-          <t>TYPE/F</t>
-        </is>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="n">
-        <v>14.54</v>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t>A1, A4, A8</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t>one pane per bay missing (ref A1 toplight)</t>
-        </is>
-      </c>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TYPE/G</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>Type G</t>
-        </is>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>TYPE/G</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="n">
-        <v>8</v>
-      </c>
-      <c r="D13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>4</v>
-      </c>
-      <c r="F13" s="3" t="n">
-        <v>6.09</v>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>A1, A5</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>one pane per bay missing (ref A1 toplight)</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TYPE/h</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>7</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>A1, D1, H1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Type H</t>
+          <t>Type J1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TYPE/h</t>
+          <t>TYPE/j (J1+J2)</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>9.859999999999999</v>
+        <v>7.72</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A1, D1, H1</t>
+          <t>A1, F1</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
@@ -1228,7 +1286,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Type J1</t>
+          <t>Type J2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1246,7 +1304,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>7.72</v>
+        <v>7.9</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1256,56 +1314,30 @@
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Type J2</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>TYPE/j (J1+J2)</t>
-        </is>
-      </c>
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>12</v>
+        <v>124</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>A1, F1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="n">
-        <v>170</v>
-      </c>
-      <c r="D17" t="n">
-        <v>124</v>
-      </c>
-      <c r="E17" t="n">
-        <v>46</v>
-      </c>
-      <c r="F17" t="n">
-        <v>130.81</v>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+        <v>106.97</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>counts reconcile once louvres are removed</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1313,6 +1345,2453 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="28" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Aplus type</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Pane ref</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Qty</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Aperture on signed-off order</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Size IKON quoted</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Height difference</t>
+        </is>
+      </c>
+      <c r="G1" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>Door Type B1</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 538</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 783</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>+245 mm</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Door Type B2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 733</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 783</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>+50 mm</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Door Type C</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 733</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 811</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>+78 mm</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Door Type C</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>771 x 2059</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 811</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>-1248 mm</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Door Type C</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>F5</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>770 x 2059</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 811</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>-1248 mm</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Type A</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1041 x 391</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>1033 x 476</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 391</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>1031 x 476</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 391</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>1031 x 476</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>1049 x 391</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1049 x 391</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 391</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 391</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 391</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>1031 x 476</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 391</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>1031 x 476</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>1049 x 391</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>1049 x 391</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 391</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 391</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 476</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>1049 x 391</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>1056 x 476</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>1049 x 391</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>1056 x 476</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 391</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>1056 x 476</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>A1</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 391</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>1056 x 476</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>+85 mm</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>louvre too tall for the aperture</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="n">
+        <v>46</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>23.84 m2</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IKON Q26-24329, 02/07/2026: 46 IKL332 28mm louvre modules with 50mm insulated</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>backing panels and insect mesh, RAL 7012 matt - GBP 10,125.91 + carriage TBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Priced against Aplus panel schedule QT50932 Rev7 (input 01/07). The frames were</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>re-input and signed off on 02/07 with these apertures 85mm shorter.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F61"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>Vetroseal line</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>Size quoted</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Size on final list</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Width shift</t>
+        </is>
+      </c>
+      <c r="F1" s="2" t="inlineStr">
+        <is>
+          <t>Height shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>Type A</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>945 x 404</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>933 x 448</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Type A</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>1033 x 1186</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>1041 x 1191</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>942 x 404</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>938 x 448</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 1186</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 1191</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>944 x 404</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>938 x 448</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Type B</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>1032 x 1186</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 1191</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>948 x 404</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>941 x 448</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>1036 x 1186</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 1191</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>936 x 404</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>940 x 448</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>1024 x 1186</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 1191</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>935 x 404</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>940 x 448</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>1023 x 1186</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 1191</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>948 x 404</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>941 x 448</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Type C</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>1036 x 1186</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 1191</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>942 x 404</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>938 x 448</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>1030 x 931</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 941</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>944 x 404</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>938 x 448</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Type D</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>1032 x 931</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>1046 x 941</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>Type E</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>945 x 953</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>925 x 933</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>948 x 404</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>941 x 448</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>1036 x 921</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 941</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>936 x 404</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>940 x 448</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>1024 x 921</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 941</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>935 x 404</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>940 x 448</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>1023 x 921</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 941</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>948 x 404</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>941 x 448</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>-7</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>Type F</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>1036 x 921</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>1048 x 941</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>968 x 1123</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>941 x 1183</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>968 x 1123</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>941 x 1183</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>968 x 1123</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>941 x 1183</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Type G</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>968 x 1123</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>941 x 1183</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>398 x 368</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>387 x 503</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>398 x 2118</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>387 x 2268</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>1962 x 313</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>1890 x 473</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>-72</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>785 x 1934</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>749 x 2059</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>-36</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>785 x 1934</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>749 x 2059</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>-36</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>398 x 368</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>387 x 503</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Door Type A</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>398 x 2118</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>387 x 2268</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>-11</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Door Type B2</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>771 x 1859</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>771 x 2059</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Door Type B2</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>770 x 1859</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>770 x 2059</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Door Type B1</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>631 x 1859</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>721 x 2059</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>90</v>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Door Type B1</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>910 x 1859</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>820 x 2059</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>-90</v>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Door Type D</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 473</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>1933 x 733</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Door Type D</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>771 x 1859</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>771 x 2059</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Door Type D</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>770 x 1859</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>770 x 2059</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="4" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>961 x 1544</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>1039 x 1477</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>78</v>
+      </c>
+      <c r="F47" s="4" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C48" s="4" t="inlineStr">
+        <is>
+          <t>1078 x 1643</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>1068 x 1477</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F48" s="4" t="n">
+        <v>-166</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>962 x 1544</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>1039 x 1477</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>1047 x 1643</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>1039 x 1477</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>-166</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>962 x 1544</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>1039 x 1477</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="F51" s="4" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>1078 x 1643</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>1068 x 1477</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F52" s="4" t="n">
+        <v>-166</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>Type H</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>962 x 1544</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>1039 x 1477</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="n">
+        <v>77</v>
+      </c>
+      <c r="F53" s="4" t="n">
+        <v>-67</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>Type J1/J2</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>870 x 707</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>880 x 648</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F54" s="4" t="n">
+        <v>-59</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>Type J1/J2</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>969 x 806</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>987 x 756</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="F55" s="4" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Type J1/J2</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>870 x 707</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>880 x 648</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F56" s="4" t="n">
+        <v>-59</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Type J1/J2</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>970 x 806</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>987 x 756</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F57" s="4" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Type J1/J2</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>870 x 707</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>880 x 648</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F58" s="4" t="n">
+        <v>-59</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>58</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Type J1/J2</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>970 x 806</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>987 x 756</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="F59" s="4" t="n">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Not one of the 124 quoted panes matches a size on the final list.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4130,7 +6609,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5997,7 +8476,7 @@
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" s="4" t="inlineStr">
+      <c r="B60" s="3" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
